--- a/marketing_forms/018_product_onboarding_form--marketing_forms.xlsx
+++ b/marketing_forms/018_product_onboarding_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>america/denver</t>
+          <t>america/indianapolis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>America/Denver</t>
+          <t>America/Indianapolis</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>america/indianapolis</t>
+          <t>america/anchorage</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>America/Indianapolis</t>
+          <t>America/Anchorage</t>
         </is>
       </c>
     </row>
@@ -1494,571 +1494,452 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>america/los_angeles</t>
+          <t>pacific</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>America/Los Angeles</t>
+          <t>Pacific</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>timezone_options_choices</t>
+          <t>product_preferences_options_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>america/indianapolis</t>
+          <t>feature_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>America/Indianapolis</t>
+          <t>Feature 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>timezone_options_choices</t>
+          <t>product_preferences_options_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>america/anchorage</t>
+          <t>feature_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>America/Anchorage</t>
+          <t>Feature 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>timezone_options_choices</t>
+          <t>product_preferences_options_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pacific</t>
+          <t>feature_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Feature 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>timezone_options_choices</t>
+          <t>product_preferences_options_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pacific</t>
+          <t>feature_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Feature 4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>timezone_options_choices</t>
+          <t>product_preferences_options_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pacific</t>
+          <t>feature_5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Feature 5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>timezone_options_choices</t>
+          <t>product_use_case_options_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pacific</t>
+          <t>use_case_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Use case 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>timezone_options_choices</t>
+          <t>product_use_case_options_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pacific</t>
+          <t>use_case_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Use case 2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>product_preferences_options_choices</t>
+          <t>product_use_case_options_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>feature_1</t>
+          <t>use_case_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Feature 1</t>
+          <t>Use case 3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>product_preferences_options_choices</t>
+          <t>product_use_case_options_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>feature_2</t>
+          <t>use_case_4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Feature 2</t>
+          <t>Use case 4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>product_preferences_options_choices</t>
+          <t>product_use_case_options_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>feature_3</t>
+          <t>use_case_5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Feature 3</t>
+          <t>Use case 5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>product_preferences_options_choices</t>
+          <t>additional_comments_options_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>feature_4</t>
+          <t>comment_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Feature 4</t>
+          <t>Comment 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>product_preferences_options_choices</t>
+          <t>additional_comments_options_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>feature_5</t>
+          <t>comment_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Feature 5</t>
+          <t>Comment 2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>product_use_case_options_choices</t>
+          <t>additional_comments_options_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>use_case_1</t>
+          <t>comment_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Use case 1</t>
+          <t>Comment 3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>product_use_case_options_choices</t>
+          <t>product_onboarding_form_comments_options_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>use_case_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Use case 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>product_use_case_options_choices</t>
+          <t>product_onboarding_form_comments_options_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>use_case_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Use case 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>product_use_case_options_choices</t>
+          <t>company_name_options_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>use_case_4</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Use case 4</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>product_use_case_options_choices</t>
+          <t>company_name_options_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>use_case_5</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Use case 5</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>additional_comments_options_choices</t>
+          <t>company_name_options_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>comment_1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Comment 1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>additional_comments_options_choices</t>
+          <t>company_type_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>comment_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Comment 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>additional_comments_options_choices</t>
+          <t>company_type_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>comment_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Comment 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>product_onboarding_form_comments_options_choices</t>
+          <t>company_type_options_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>product_onboarding_form_comments_options_choices</t>
+          <t>company_type_options_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>company_name_options_choices</t>
+          <t>company_size_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>company_name_options_choices</t>
+          <t>company_size_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>company_name_options_choices</t>
+          <t>company_size_options_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>company_type_choices</t>
+          <t>company_size_options_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>company_type_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>company_type_options_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>company_type_options_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>company_size_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>company_size_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>company_size_options_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>company_size_options_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
